--- a/artfynd/A 41447-2020 artfynd.xlsx
+++ b/artfynd/A 41447-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41447-2020 artfynd.xlsx
+++ b/artfynd/A 41447-2020 artfynd.xlsx
@@ -3802,7 +3802,7 @@
         <v>100511761</v>
       </c>
       <c r="B27" t="n">
-        <v>10336</v>
+        <v>10387</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517779.842498992</v>
+        <v>517780</v>
       </c>
       <c r="R27" t="n">
-        <v>7123565.663391723</v>
+        <v>7123566</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3886,19 +3886,9 @@
           <t>2021-05-21</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4939,7 +4929,7 @@
         <v>100352351</v>
       </c>
       <c r="B35" t="n">
-        <v>11723</v>
+        <v>11794</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4984,10 +4974,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517817.0564297041</v>
+        <v>517817</v>
       </c>
       <c r="R35" t="n">
-        <v>7123609.388006947</v>
+        <v>7123609</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5794,7 +5784,7 @@
         <v>100429529</v>
       </c>
       <c r="B41" t="n">
-        <v>11723</v>
+        <v>11794</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5840,10 +5830,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517779.842498992</v>
+        <v>517780</v>
       </c>
       <c r="R41" t="n">
-        <v>7123565.663391723</v>
+        <v>7123566</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5873,19 +5863,9 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
